--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/80.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/80.xlsx
@@ -426,13 +426,13 @@
         <v>-4.738151617278511</v>
       </c>
       <c r="E2">
-        <v>-6.060106994416565</v>
+        <v>-7.902600287661576</v>
       </c>
       <c r="F2">
-        <v>-1.827372839251397</v>
+        <v>-2.082514969518062</v>
       </c>
       <c r="G2">
-        <v>-9.49037977685701</v>
+        <v>-8.07873973346369</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.74087941926676</v>
       </c>
       <c r="E3">
-        <v>-6.773840513799675</v>
+        <v>-8.170249838278826</v>
       </c>
       <c r="F3">
-        <v>-1.028025631674167</v>
+        <v>-2.293845576218064</v>
       </c>
       <c r="G3">
-        <v>-9.391959927261221</v>
+        <v>-8.197639569004467</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.678407311608425</v>
       </c>
       <c r="E4">
-        <v>-7.301260973150977</v>
+        <v>-9.025038873887087</v>
       </c>
       <c r="F4">
-        <v>-1.519509265633558</v>
+        <v>-1.965388788966629</v>
       </c>
       <c r="G4">
-        <v>-9.026168502600338</v>
+        <v>-7.60466637151409</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.524347387720064</v>
       </c>
       <c r="E5">
-        <v>-8.882658483249315</v>
+        <v>-9.867264445237744</v>
       </c>
       <c r="F5">
-        <v>-0.9745636278648897</v>
+        <v>-2.156224757753967</v>
       </c>
       <c r="G5">
-        <v>-9.17514411583074</v>
+        <v>-7.47132520226757</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.275024224266009</v>
       </c>
       <c r="E6">
-        <v>-10.3940909953696</v>
+        <v>-9.838279183401765</v>
       </c>
       <c r="F6">
-        <v>-0.9301482244615858</v>
+        <v>-1.769024296133006</v>
       </c>
       <c r="G6">
-        <v>-8.164167212601804</v>
+        <v>-7.261267303211186</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.920621675925066</v>
       </c>
       <c r="E7">
-        <v>-10.85564567632044</v>
+        <v>-11.41676944557272</v>
       </c>
       <c r="F7">
-        <v>-0.7985744880379263</v>
+        <v>-1.919186597075486</v>
       </c>
       <c r="G7">
-        <v>-8.545882873896183</v>
+        <v>-6.909197952121195</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.451969356023585</v>
       </c>
       <c r="E8">
-        <v>-9.452765648597206</v>
+        <v>-11.89208786885405</v>
       </c>
       <c r="F8">
-        <v>-1.280608935033584</v>
+        <v>-1.55036015281602</v>
       </c>
       <c r="G8">
-        <v>-8.150784535827757</v>
+        <v>-6.460071560111976</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.867838966060318</v>
       </c>
       <c r="E9">
-        <v>-11.94119543955883</v>
+        <v>-13.07817857184389</v>
       </c>
       <c r="F9">
-        <v>-0.8827647806540513</v>
+        <v>-1.873196467239461</v>
       </c>
       <c r="G9">
-        <v>-7.385105362146053</v>
+        <v>-5.975144027524821</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.169184364951588</v>
       </c>
       <c r="E10">
-        <v>-11.51806626978529</v>
+        <v>-13.40230349005616</v>
       </c>
       <c r="F10">
-        <v>-0.8236939011604185</v>
+        <v>-1.666684473721544</v>
       </c>
       <c r="G10">
-        <v>-7.049447151555801</v>
+        <v>-5.490276542063262</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.376236021558296</v>
       </c>
       <c r="E11">
-        <v>-13.01191408515625</v>
+        <v>-14.13502549161638</v>
       </c>
       <c r="F11">
-        <v>-0.7866194896807239</v>
+        <v>-1.590340477144736</v>
       </c>
       <c r="G11">
-        <v>-6.077117100509115</v>
+        <v>-5.463665222446044</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.5260529321639826</v>
       </c>
       <c r="E12">
-        <v>-13.60880115712663</v>
+        <v>-14.57279473130993</v>
       </c>
       <c r="F12">
-        <v>-0.5774161304711115</v>
+        <v>-1.503174688817755</v>
       </c>
       <c r="G12">
-        <v>-5.307015325490065</v>
+        <v>-4.670701157042615</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.3383259171959855</v>
       </c>
       <c r="E13">
-        <v>-14.52347950003892</v>
+        <v>-16.13161123143518</v>
       </c>
       <c r="F13">
-        <v>-1.05068645034515</v>
+        <v>-1.219887947673574</v>
       </c>
       <c r="G13">
-        <v>-5.364417766814872</v>
+        <v>-4.227597752805094</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>1.16276966796155</v>
       </c>
       <c r="E14">
-        <v>-14.88073873820067</v>
+        <v>-16.16738699378725</v>
       </c>
       <c r="F14">
-        <v>-0.1638122862533184</v>
+        <v>-1.05636159542173</v>
       </c>
       <c r="G14">
-        <v>-5.07990665350912</v>
+        <v>-3.83494959853543</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>1.906127790422149</v>
       </c>
       <c r="E15">
-        <v>-16.88651968789264</v>
+        <v>-17.2259159641463</v>
       </c>
       <c r="F15">
-        <v>-0.2744747159607072</v>
+        <v>-1.140868324385724</v>
       </c>
       <c r="G15">
-        <v>-4.822056463967816</v>
+        <v>-3.402351830532549</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>2.540383897785781</v>
       </c>
       <c r="E16">
-        <v>-16.58701915962528</v>
+        <v>-17.71157173041513</v>
       </c>
       <c r="F16">
-        <v>0.141538020664427</v>
+        <v>-0.6387012360324273</v>
       </c>
       <c r="G16">
-        <v>-4.229837771664269</v>
+        <v>-2.899203911444014</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.049225788174385</v>
       </c>
       <c r="E17">
-        <v>-16.98750502125585</v>
+        <v>-18.94078522659066</v>
       </c>
       <c r="F17">
-        <v>0.02627235329968137</v>
+        <v>-0.6429491040739832</v>
       </c>
       <c r="G17">
-        <v>-2.977868256718849</v>
+        <v>-2.872866720008864</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>3.440854444280571</v>
       </c>
       <c r="E18">
-        <v>-19.0251826339225</v>
+        <v>-19.6706165930688</v>
       </c>
       <c r="F18">
-        <v>0.02646701963933925</v>
+        <v>-0.3018174671923132</v>
       </c>
       <c r="G18">
-        <v>-3.250038380342409</v>
+        <v>-2.159611297716714</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.730047107364054</v>
       </c>
       <c r="E19">
-        <v>-20.6456826286441</v>
+        <v>-20.8351064439582</v>
       </c>
       <c r="F19">
-        <v>1.482750167639315</v>
+        <v>0.2366718750389362</v>
       </c>
       <c r="G19">
-        <v>-2.382344361762953</v>
+        <v>-1.491962972686723</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.940222145413083</v>
       </c>
       <c r="E20">
-        <v>-21.25011193238037</v>
+        <v>-21.6582687753279</v>
       </c>
       <c r="F20">
-        <v>0.8545743150743659</v>
+        <v>0.4397809352661526</v>
       </c>
       <c r="G20">
-        <v>-3.371002009482461</v>
+        <v>-0.9014099354323061</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>4.099504837931321</v>
       </c>
       <c r="E21">
-        <v>-21.3681129725414</v>
+        <v>-22.63599286615108</v>
       </c>
       <c r="F21">
-        <v>0.9233818250205039</v>
+        <v>0.681173823381151</v>
       </c>
       <c r="G21">
-        <v>-2.018589317883139</v>
+        <v>-0.9391456377522576</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>4.226914170200367</v>
       </c>
       <c r="E22">
-        <v>-22.09185157800602</v>
+        <v>-22.39519797996017</v>
       </c>
       <c r="F22">
-        <v>2.023071030198154</v>
+        <v>0.8196205241458379</v>
       </c>
       <c r="G22">
-        <v>-2.262378037056707</v>
+        <v>-0.8524271454138387</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.344609116330441</v>
       </c>
       <c r="E23">
-        <v>-22.75792699743672</v>
+        <v>-23.08959414741488</v>
       </c>
       <c r="F23">
-        <v>1.248923587381487</v>
+        <v>0.495361902891791</v>
       </c>
       <c r="G23">
-        <v>-2.132973870653585</v>
+        <v>-0.8018883516190677</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.467092943925286</v>
       </c>
       <c r="E24">
-        <v>-22.90277854881277</v>
+        <v>-23.37098252109466</v>
       </c>
       <c r="F24">
-        <v>1.552506986629061</v>
+        <v>0.8579557108125934</v>
       </c>
       <c r="G24">
-        <v>-1.633222530278089</v>
+        <v>-0.5175260507550086</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.603196935004348</v>
       </c>
       <c r="E25">
-        <v>-22.90663688213353</v>
+        <v>-23.31235579003339</v>
       </c>
       <c r="F25">
-        <v>1.743347925620817</v>
+        <v>0.804907062337313</v>
       </c>
       <c r="G25">
-        <v>-0.5857656928775277</v>
+        <v>-0.4634914699527369</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>4.762818765165198</v>
       </c>
       <c r="E26">
-        <v>-23.48649578767212</v>
+        <v>-23.48106754047057</v>
       </c>
       <c r="F26">
-        <v>1.689030218284448</v>
+        <v>1.145081106501347</v>
       </c>
       <c r="G26">
-        <v>-1.333963320777138</v>
+        <v>-0.4371908289418617</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>4.946570352749194</v>
       </c>
       <c r="E27">
-        <v>-23.50255625586523</v>
+        <v>-23.96521569102848</v>
       </c>
       <c r="F27">
-        <v>1.873214396827307</v>
+        <v>1.070299410846219</v>
       </c>
       <c r="G27">
-        <v>-1.411011615150073</v>
+        <v>-0.2457710355214356</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>5.155320937854682</v>
       </c>
       <c r="E28">
-        <v>-22.51790460855223</v>
+        <v>-23.94138456444662</v>
       </c>
       <c r="F28">
-        <v>1.864470150523355</v>
+        <v>1.020882325064811</v>
       </c>
       <c r="G28">
-        <v>-1.926842531462236</v>
+        <v>-0.3004583024714856</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>5.385146786827996</v>
       </c>
       <c r="E29">
-        <v>-23.53533755285211</v>
+        <v>-23.84665812054993</v>
       </c>
       <c r="F29">
-        <v>2.34701570020654</v>
+        <v>0.9069967177931297</v>
       </c>
       <c r="G29">
-        <v>-3.20754851212204</v>
+        <v>-0.5863139492416615</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>5.628325954980673</v>
       </c>
       <c r="E30">
-        <v>-23.12291951508531</v>
+        <v>-23.16777419739346</v>
       </c>
       <c r="F30">
-        <v>2.070586184422734</v>
+        <v>0.8559146135320954</v>
       </c>
       <c r="G30">
-        <v>-1.223862999880708</v>
+        <v>-0.4525185104362878</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>5.879081671609238</v>
       </c>
       <c r="E31">
-        <v>-22.82274616658332</v>
+        <v>-22.96582014351234</v>
       </c>
       <c r="F31">
-        <v>1.26980010266684</v>
+        <v>0.9883291428695964</v>
       </c>
       <c r="G31">
-        <v>-1.082587777821795</v>
+        <v>-0.5642766541480742</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>6.124891395511532</v>
       </c>
       <c r="E32">
-        <v>-23.5646259991148</v>
+        <v>-23.21292791091699</v>
       </c>
       <c r="F32">
-        <v>1.710405410746286</v>
+        <v>0.8194333131128052</v>
       </c>
       <c r="G32">
-        <v>-1.353956402855883</v>
+        <v>-0.2264489148026061</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>6.353570766009042</v>
       </c>
       <c r="E33">
-        <v>-22.30576688050264</v>
+        <v>-22.36220902240706</v>
       </c>
       <c r="F33">
-        <v>1.474695123014492</v>
+        <v>0.958194793490556</v>
       </c>
       <c r="G33">
-        <v>-1.312333301839764</v>
+        <v>-0.4477042974102749</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>6.55504454107916</v>
       </c>
       <c r="E34">
-        <v>-21.3541291100107</v>
+        <v>-22.06358482172924</v>
       </c>
       <c r="F34">
-        <v>1.263673497355735</v>
+        <v>1.090943983258788</v>
       </c>
       <c r="G34">
-        <v>-0.3334267851680641</v>
+        <v>-0.6715286526955991</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>6.718389078643529</v>
       </c>
       <c r="E35">
-        <v>-22.43515602611635</v>
+        <v>-21.85408022965959</v>
       </c>
       <c r="F35">
-        <v>1.546645458886852</v>
+        <v>0.9226760559933188</v>
       </c>
       <c r="G35">
-        <v>-1.798521824064427</v>
+        <v>-0.9411063069401836</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>6.841347150260752</v>
       </c>
       <c r="E36">
-        <v>-20.6644343777757</v>
+        <v>-21.72086597641571</v>
       </c>
       <c r="F36">
-        <v>1.577212216050154</v>
+        <v>0.9369703638960271</v>
       </c>
       <c r="G36">
-        <v>-2.045811551734677</v>
+        <v>-0.8441876354842851</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>6.922019654515378</v>
       </c>
       <c r="E37">
-        <v>-19.50705067146308</v>
+        <v>-20.77097670789153</v>
       </c>
       <c r="F37">
-        <v>1.790245117762908</v>
+        <v>0.7135952951593207</v>
       </c>
       <c r="G37">
-        <v>-1.624299005265664</v>
+        <v>-0.8722192001590685</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>6.959969352279715</v>
       </c>
       <c r="E38">
-        <v>-19.95045581892442</v>
+        <v>-20.26006941676775</v>
       </c>
       <c r="F38">
-        <v>1.604296516652086</v>
+        <v>0.959057952324273</v>
       </c>
       <c r="G38">
-        <v>-2.739293194493735</v>
+        <v>-0.8977157318358808</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>6.954909093929386</v>
       </c>
       <c r="E39">
-        <v>-20.26839660547402</v>
+        <v>-19.95446782106421</v>
       </c>
       <c r="F39">
-        <v>1.641100880358468</v>
+        <v>0.9768231196447112</v>
       </c>
       <c r="G39">
-        <v>-1.717011767185279</v>
+        <v>-0.896313761990453</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>6.90091129847626</v>
       </c>
       <c r="E40">
-        <v>-18.75967614034886</v>
+        <v>-19.32994943414974</v>
       </c>
       <c r="F40">
-        <v>1.615582194147827</v>
+        <v>1.259311314612593</v>
       </c>
       <c r="G40">
-        <v>-2.137096236362953</v>
+        <v>-1.261925045274549</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>6.800047103351178</v>
       </c>
       <c r="E41">
-        <v>-19.02906588651121</v>
+        <v>-18.20950023614882</v>
       </c>
       <c r="F41">
-        <v>1.359538800146916</v>
+        <v>1.00061880165753</v>
       </c>
       <c r="G41">
-        <v>-2.224804200901404</v>
+        <v>-1.806377554539087</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>6.663138894930245</v>
       </c>
       <c r="E42">
-        <v>-18.6086155380422</v>
+        <v>-18.23760917039526</v>
       </c>
       <c r="F42">
-        <v>2.098603226720218</v>
+        <v>0.7956989302877937</v>
       </c>
       <c r="G42">
-        <v>-2.756484947626216</v>
+        <v>-1.422384018588962</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>6.506102345409239</v>
       </c>
       <c r="E43">
-        <v>-17.34814082022468</v>
+        <v>-16.91511870107541</v>
       </c>
       <c r="F43">
-        <v>2.138272084905481</v>
+        <v>0.8406842504642237</v>
       </c>
       <c r="G43">
-        <v>-2.053129468823568</v>
+        <v>-1.81517837455573</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>6.346068491028667</v>
       </c>
       <c r="E44">
-        <v>-15.00197097677242</v>
+        <v>-16.78723301796129</v>
       </c>
       <c r="F44">
-        <v>1.92645025633562</v>
+        <v>0.716139211453318</v>
       </c>
       <c r="G44">
-        <v>-2.835010923437721</v>
+        <v>-1.694862210074274</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>6.188749536371637</v>
       </c>
       <c r="E45">
-        <v>-15.31354489036105</v>
+        <v>-16.2195513280271</v>
       </c>
       <c r="F45">
-        <v>1.686056379308398</v>
+        <v>0.9451148722003517</v>
       </c>
       <c r="G45">
-        <v>-1.915026301442857</v>
+        <v>-1.632475857325031</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>6.037720128398022</v>
       </c>
       <c r="E46">
-        <v>-15.84925515951671</v>
+        <v>-15.51161984486478</v>
       </c>
       <c r="F46">
-        <v>1.767213190495471</v>
+        <v>0.8498774719004927</v>
       </c>
       <c r="G46">
-        <v>-2.488379753331019</v>
+        <v>-1.724327073529578</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>5.891230299329635</v>
       </c>
       <c r="E47">
-        <v>-15.25039115895571</v>
+        <v>-14.93689430852368</v>
       </c>
       <c r="F47">
-        <v>2.313002934647592</v>
+        <v>1.248759570635733</v>
       </c>
       <c r="G47">
-        <v>-2.408370874591761</v>
+        <v>-2.19510698117749</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>5.740892454529033</v>
       </c>
       <c r="E48">
-        <v>-12.84475148254322</v>
+        <v>-14.62892953557632</v>
       </c>
       <c r="F48">
-        <v>1.114517662807656</v>
+        <v>0.7254202398342837</v>
       </c>
       <c r="G48">
-        <v>-4.02302502813464</v>
+        <v>-2.38937248620223</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>5.580157944126701</v>
       </c>
       <c r="E49">
-        <v>-14.27069429275323</v>
+        <v>-13.69542053251725</v>
       </c>
       <c r="F49">
-        <v>1.642187698390941</v>
+        <v>1.069242414040247</v>
       </c>
       <c r="G49">
-        <v>-2.751393995673545</v>
+        <v>-2.253634653421068</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>5.39639794881426</v>
       </c>
       <c r="E50">
-        <v>-12.31438639636262</v>
+        <v>-13.21692905578376</v>
       </c>
       <c r="F50">
-        <v>2.066349913524817</v>
+        <v>1.01729549421069</v>
       </c>
       <c r="G50">
-        <v>-3.829302557984851</v>
+        <v>-2.222558960553047</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>5.179778559720514</v>
       </c>
       <c r="E51">
-        <v>-11.60961550701849</v>
+        <v>-12.23623126565199</v>
       </c>
       <c r="F51">
-        <v>1.644111167500242</v>
+        <v>1.024450931836072</v>
       </c>
       <c r="G51">
-        <v>-2.988525316139774</v>
+        <v>-2.090008846917634</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>4.923224331619346</v>
       </c>
       <c r="E52">
-        <v>-11.66198334861325</v>
+        <v>-11.81756264484133</v>
       </c>
       <c r="F52">
-        <v>1.439444776555762</v>
+        <v>1.084684839163235</v>
       </c>
       <c r="G52">
-        <v>-3.334012980115568</v>
+        <v>-2.671223250769638</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>4.617458369019587</v>
       </c>
       <c r="E53">
-        <v>-11.80708409266879</v>
+        <v>-11.28754642841201</v>
       </c>
       <c r="F53">
-        <v>1.518883553749429</v>
+        <v>0.9174755654385435</v>
       </c>
       <c r="G53">
-        <v>-3.375586476984456</v>
+        <v>-2.777942657420576</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>4.262161819768855</v>
       </c>
       <c r="E54">
-        <v>-11.84211227698239</v>
+        <v>-11.58080052684683</v>
       </c>
       <c r="F54">
-        <v>1.281067556079719</v>
+        <v>1.001076060463875</v>
       </c>
       <c r="G54">
-        <v>-3.815750182812383</v>
+        <v>-3.499108635823799</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>3.852188369773248</v>
       </c>
       <c r="E55">
-        <v>-12.00883048598366</v>
+        <v>-11.16930865520547</v>
       </c>
       <c r="F55">
-        <v>1.234750221119588</v>
+        <v>1.090330991380716</v>
       </c>
       <c r="G55">
-        <v>-3.908123547935153</v>
+        <v>-3.656421661905921</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>3.384973413427765</v>
       </c>
       <c r="E56">
-        <v>-12.49912954251364</v>
+        <v>-10.13912535213837</v>
       </c>
       <c r="F56">
-        <v>1.946886080162683</v>
+        <v>0.8957806231592245</v>
       </c>
       <c r="G56">
-        <v>-4.027431965004439</v>
+        <v>-3.327227654923265</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>2.865011105717179</v>
       </c>
       <c r="E57">
-        <v>-10.01442102889907</v>
+        <v>-10.76192846277568</v>
       </c>
       <c r="F57">
-        <v>1.369045144461444</v>
+        <v>0.9049142021424917</v>
       </c>
       <c r="G57">
-        <v>-4.015560909348647</v>
+        <v>-3.982542822504837</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>2.293219061293378</v>
       </c>
       <c r="E58">
-        <v>-9.448168043660621</v>
+        <v>-9.730108794446606</v>
       </c>
       <c r="F58">
-        <v>1.363731995939887</v>
+        <v>1.129214557268125</v>
       </c>
       <c r="G58">
-        <v>-5.360893261616869</v>
+        <v>-4.29800953442742</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.680022733257179</v>
       </c>
       <c r="E59">
-        <v>-9.694794038551588</v>
+        <v>-9.431949753437165</v>
       </c>
       <c r="F59">
-        <v>2.031238732789757</v>
+        <v>0.9678601843464206</v>
       </c>
       <c r="G59">
-        <v>-5.710119511847139</v>
+        <v>-4.208265189107901</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.034547323045169</v>
       </c>
       <c r="E60">
-        <v>-8.771215363770192</v>
+        <v>-8.565930434406567</v>
       </c>
       <c r="F60">
-        <v>1.514231442415307</v>
+        <v>0.8927438282605614</v>
       </c>
       <c r="G60">
-        <v>-4.74158026194675</v>
+        <v>-4.163843369890108</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.3643837030482124</v>
       </c>
       <c r="E61">
-        <v>-9.376039222582323</v>
+        <v>-8.790378280822951</v>
       </c>
       <c r="F61">
-        <v>1.563721424528161</v>
+        <v>0.7314772622835537</v>
       </c>
       <c r="G61">
-        <v>-5.566126504668876</v>
+        <v>-4.532712862423913</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.3133944160103485</v>
       </c>
       <c r="E62">
-        <v>-8.179872828918455</v>
+        <v>-8.210697963371333</v>
       </c>
       <c r="F62">
-        <v>1.571869246302097</v>
+        <v>1.104723046636955</v>
       </c>
       <c r="G62">
-        <v>-4.742152015012203</v>
+        <v>-4.604286425389284</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.9897904966461718</v>
       </c>
       <c r="E63">
-        <v>-7.068232592137496</v>
+        <v>-7.75947647219666</v>
       </c>
       <c r="F63">
-        <v>1.589733817710871</v>
+        <v>0.9495830859710523</v>
       </c>
       <c r="G63">
-        <v>-6.050946996727795</v>
+        <v>-4.946356624695311</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.651382571383956</v>
       </c>
       <c r="E64">
-        <v>-7.330005348730115</v>
+        <v>-8.828828711268214</v>
       </c>
       <c r="F64">
-        <v>1.409113275734856</v>
+        <v>0.8838686999069676</v>
       </c>
       <c r="G64">
-        <v>-5.575026532979981</v>
+        <v>-4.840133259516684</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.282241188645488</v>
       </c>
       <c r="E65">
-        <v>-7.957123645933925</v>
+        <v>-7.503061358213071</v>
       </c>
       <c r="F65">
-        <v>1.284743850613344</v>
+        <v>1.124327189591608</v>
       </c>
       <c r="G65">
-        <v>-5.306999661022518</v>
+        <v>-5.422149161958161</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.872425237929172</v>
       </c>
       <c r="E66">
-        <v>-7.14481365575601</v>
+        <v>-7.689428409992102</v>
       </c>
       <c r="F66">
-        <v>1.261735117633184</v>
+        <v>0.8713653223291118</v>
       </c>
       <c r="G66">
-        <v>-5.79168700510729</v>
+        <v>-5.456248097062691</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.405404769811185</v>
       </c>
       <c r="E67">
-        <v>-6.741898165500419</v>
+        <v>-7.041178573567564</v>
       </c>
       <c r="F67">
-        <v>0.7774135482383975</v>
+        <v>0.756389583555346</v>
       </c>
       <c r="G67">
-        <v>-6.005311181275135</v>
+        <v>-5.502604478022499</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.869607945896977</v>
       </c>
       <c r="E68">
-        <v>-7.976336401522582</v>
+        <v>-7.516131514252306</v>
       </c>
       <c r="F68">
-        <v>1.495540160338539</v>
+        <v>0.6117847995182475</v>
       </c>
       <c r="G68">
-        <v>-6.057014367157542</v>
+        <v>-5.307594910789292</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.256054556423921</v>
       </c>
       <c r="E69">
-        <v>-6.862320527863822</v>
+        <v>-7.186686332332932</v>
       </c>
       <c r="F69">
-        <v>1.096243877901899</v>
+        <v>0.798036583098494</v>
       </c>
       <c r="G69">
-        <v>-5.723507410110368</v>
+        <v>-5.165565183543547</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.555498187927634</v>
       </c>
       <c r="E70">
-        <v>-5.095166488051201</v>
+        <v>-7.109403376000522</v>
       </c>
       <c r="F70">
-        <v>1.297813831494714</v>
+        <v>0.4799492989953034</v>
       </c>
       <c r="G70">
-        <v>-5.109541215362847</v>
+        <v>-5.42500792728543</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.771073210014583</v>
       </c>
       <c r="E71">
-        <v>-7.162244683686316</v>
+        <v>-6.937701313409461</v>
       </c>
       <c r="F71">
-        <v>1.134241090668312</v>
+        <v>0.5812412366422242</v>
       </c>
       <c r="G71">
-        <v>-6.339068769803058</v>
+        <v>-5.352063723409724</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.907610262820754</v>
       </c>
       <c r="E72">
-        <v>-5.36431119474539</v>
+        <v>-6.534233446047667</v>
       </c>
       <c r="F72">
-        <v>1.194594282901479</v>
+        <v>0.7208956970801929</v>
       </c>
       <c r="G72">
-        <v>-6.137122454191263</v>
+        <v>-5.238919274320057</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.975410878799212</v>
       </c>
       <c r="E73">
-        <v>-7.964811240096183</v>
+        <v>-6.787616715764131</v>
       </c>
       <c r="F73">
-        <v>1.470614585188302</v>
+        <v>0.6960521303028329</v>
       </c>
       <c r="G73">
-        <v>-5.869278334355178</v>
+        <v>-5.281664995510354</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.988443136523331</v>
       </c>
       <c r="E74">
-        <v>-8.459533466687109</v>
+        <v>-7.459319736539976</v>
       </c>
       <c r="F74">
-        <v>0.9941061771367201</v>
+        <v>0.4203681451815461</v>
       </c>
       <c r="G74">
-        <v>-5.283980725962672</v>
+        <v>-5.13435895344597</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.958288705484086</v>
       </c>
       <c r="E75">
-        <v>-7.146096998055382</v>
+        <v>-7.458086232776502</v>
       </c>
       <c r="F75">
-        <v>0.8116284354436283</v>
+        <v>0.1994268198742648</v>
       </c>
       <c r="G75">
-        <v>-4.971385833090314</v>
+        <v>-4.86896632278094</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.895703643319201</v>
       </c>
       <c r="E76">
-        <v>-7.727459366093557</v>
+        <v>-8.358543980112579</v>
       </c>
       <c r="F76">
-        <v>0.9635278228297792</v>
+        <v>0.3661705511185829</v>
       </c>
       <c r="G76">
-        <v>-5.642595213742585</v>
+        <v>-5.318546984349012</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.803091763748244</v>
       </c>
       <c r="E77">
-        <v>-8.490462431423108</v>
+        <v>-8.731265624036666</v>
       </c>
       <c r="F77">
-        <v>0.985830786782753</v>
+        <v>0.4499392047266829</v>
       </c>
       <c r="G77">
-        <v>-6.110469362660587</v>
+        <v>-4.678280148590616</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.678902220591851</v>
       </c>
       <c r="E78">
-        <v>-8.671372163521314</v>
+        <v>-9.151533231207392</v>
       </c>
       <c r="F78">
-        <v>0.4402671869315959</v>
+        <v>0.4947994414252901</v>
       </c>
       <c r="G78">
-        <v>-4.6161209306208</v>
+        <v>-4.40560354051638</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.515781561671323</v>
       </c>
       <c r="E79">
-        <v>-8.555107165694064</v>
+        <v>-9.117858993785681</v>
       </c>
       <c r="F79">
-        <v>1.273527755979438</v>
+        <v>0.5507506892799799</v>
       </c>
       <c r="G79">
-        <v>-5.409476607712897</v>
+        <v>-4.430841608478673</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.303087932728308</v>
       </c>
       <c r="E80">
-        <v>-10.30987217612472</v>
+        <v>-10.16328873562622</v>
       </c>
       <c r="F80">
-        <v>1.205947886524249</v>
+        <v>0.3313426720352805</v>
       </c>
       <c r="G80">
-        <v>-4.564391637292482</v>
+        <v>-4.371742183169641</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.032154380444156</v>
       </c>
       <c r="E81">
-        <v>-10.65460532893079</v>
+        <v>-10.33346241644975</v>
       </c>
       <c r="F81">
-        <v>0.6650803014795621</v>
+        <v>0.5876942187100322</v>
       </c>
       <c r="G81">
-        <v>-4.30283941192098</v>
+        <v>-3.811304084773717</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.690510794454433</v>
       </c>
       <c r="E82">
-        <v>-11.41515799957869</v>
+        <v>-10.79327690185549</v>
       </c>
       <c r="F82">
-        <v>1.099575571595959</v>
+        <v>0.4665860760533418</v>
       </c>
       <c r="G82">
-        <v>-3.726462717796308</v>
+        <v>-3.671872048396129</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.274584094488958</v>
       </c>
       <c r="E83">
-        <v>-11.01453923518573</v>
+        <v>-12.48201831185535</v>
       </c>
       <c r="F83">
-        <v>1.295098443148337</v>
+        <v>0.453140844738503</v>
       </c>
       <c r="G83">
-        <v>-4.411258413300732</v>
+        <v>-3.698660898645543</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.782753439338786</v>
       </c>
       <c r="E84">
-        <v>-13.42390018894526</v>
+        <v>-12.90684199184941</v>
       </c>
       <c r="F84">
-        <v>1.398367693785741</v>
+        <v>0.5262575219140042</v>
       </c>
       <c r="G84">
-        <v>-4.250567083717709</v>
+        <v>-3.599042717282433</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.217410298735997</v>
       </c>
       <c r="E85">
-        <v>-13.36952634628061</v>
+        <v>-14.00150805394579</v>
       </c>
       <c r="F85">
-        <v>0.9571063187232774</v>
+        <v>0.6640846038613971</v>
       </c>
       <c r="G85">
-        <v>-4.40881475636345</v>
+        <v>-3.358110152691543</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.594034479695688</v>
       </c>
       <c r="E86">
-        <v>-16.13901225401602</v>
+        <v>-15.02552383819552</v>
       </c>
       <c r="F86">
-        <v>0.6588600906519406</v>
+        <v>0.5630900501120814</v>
       </c>
       <c r="G86">
-        <v>-4.126300862669899</v>
+        <v>-3.301266410709234</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.9260869475956328</v>
       </c>
       <c r="E87">
-        <v>-14.89399994196085</v>
+        <v>-15.97438726352247</v>
       </c>
       <c r="F87">
-        <v>1.385549536594821</v>
+        <v>0.6700422222223311</v>
       </c>
       <c r="G87">
-        <v>-3.961649033542157</v>
+        <v>-3.195489482855688</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.2348391553526583</v>
       </c>
       <c r="E88">
-        <v>-17.67473689917523</v>
+        <v>-17.89839563543989</v>
       </c>
       <c r="F88">
-        <v>0.8221023128846252</v>
+        <v>0.5715791592559707</v>
       </c>
       <c r="G88">
-        <v>-2.762581036246465</v>
+        <v>-2.602889621841839</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.4551762645244589</v>
       </c>
       <c r="E89">
-        <v>-18.93875845946414</v>
+        <v>-18.67924920304355</v>
       </c>
       <c r="F89">
-        <v>0.9332526509922628</v>
+        <v>0.4814544425661901</v>
       </c>
       <c r="G89">
-        <v>-3.64689766563754</v>
+        <v>-2.746462299140932</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.124034491968715</v>
       </c>
       <c r="E90">
-        <v>-20.29182902376871</v>
+        <v>-21.00295432643982</v>
       </c>
       <c r="F90">
-        <v>1.0528357692604</v>
+        <v>0.5965362123675142</v>
       </c>
       <c r="G90">
-        <v>-2.885630650314817</v>
+        <v>-2.264539733578148</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.745731650960794</v>
       </c>
       <c r="E91">
-        <v>-21.71067814903591</v>
+        <v>-22.03362355523193</v>
       </c>
       <c r="F91">
-        <v>1.55616671381463</v>
+        <v>0.6183844026163512</v>
       </c>
       <c r="G91">
-        <v>-2.652903655973796</v>
+        <v>-2.32455291949407</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.300229712635435</v>
       </c>
       <c r="E92">
-        <v>-24.1714018672496</v>
+        <v>-23.99754428798095</v>
       </c>
       <c r="F92">
-        <v>0.8856629437014313</v>
+        <v>0.4881667036310745</v>
       </c>
       <c r="G92">
-        <v>-2.799791978903603</v>
+        <v>-2.264129846677343</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.770556079122952</v>
       </c>
       <c r="E93">
-        <v>-26.37818578542929</v>
+        <v>-26.08295475840385</v>
       </c>
       <c r="F93">
-        <v>1.565273785041007</v>
+        <v>0.5558650296248641</v>
       </c>
       <c r="G93">
-        <v>-2.451534314916637</v>
+        <v>-2.14252919585706</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>3.138689795817986</v>
       </c>
       <c r="E94">
-        <v>-29.55772863029334</v>
+        <v>-28.38819470424994</v>
       </c>
       <c r="F94">
-        <v>1.000981626579956</v>
+        <v>0.2360332037713778</v>
       </c>
       <c r="G94">
-        <v>-2.841088736845833</v>
+        <v>-2.022246971055289</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>3.397767839313833</v>
       </c>
       <c r="E95">
-        <v>-31.31285912332059</v>
+        <v>-30.33459303841951</v>
       </c>
       <c r="F95">
-        <v>1.079058567763421</v>
+        <v>0.3739721153181487</v>
       </c>
       <c r="G95">
-        <v>-3.120226937783074</v>
+        <v>-2.07184850754185</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>3.536277692377462</v>
       </c>
       <c r="E96">
-        <v>-33.43196875043315</v>
+        <v>-32.55731075184691</v>
       </c>
       <c r="F96">
-        <v>0.9565612529722354</v>
+        <v>0.1936141658088207</v>
       </c>
       <c r="G96">
-        <v>-2.512106200175057</v>
+        <v>-2.275606679899878</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>3.557964822907505</v>
       </c>
       <c r="E97">
-        <v>-34.60996899776222</v>
+        <v>-35.26743688672222</v>
       </c>
       <c r="F97">
-        <v>1.333208313881531</v>
+        <v>0.03393972197999359</v>
       </c>
       <c r="G97">
-        <v>-2.85233843528894</v>
+        <v>-1.543211889010276</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>3.454433820122038</v>
       </c>
       <c r="E98">
-        <v>-37.03730920334694</v>
+        <v>-37.16399876159951</v>
       </c>
       <c r="F98">
-        <v>0.5989740976339532</v>
+        <v>-0.0654221196184043</v>
       </c>
       <c r="G98">
-        <v>-2.549724418988408</v>
+        <v>-2.249274709953909</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>3.251234348412239</v>
       </c>
       <c r="E99">
-        <v>-39.66485288423935</v>
+        <v>-39.11055699440509</v>
       </c>
       <c r="F99">
-        <v>0.752439927778798</v>
+        <v>0.02280977755597944</v>
       </c>
       <c r="G99">
-        <v>-2.031494228397012</v>
+        <v>-1.630332436015727</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>2.934342565788809</v>
       </c>
       <c r="E100">
-        <v>-43.33829146664068</v>
+        <v>-42.399391595282</v>
       </c>
       <c r="F100">
-        <v>0.6455639654696058</v>
+        <v>-0.1763786197537869</v>
       </c>
       <c r="G100">
-        <v>-3.049279953519571</v>
+        <v>-1.969214916176004</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>2.571971422834202</v>
       </c>
       <c r="E101">
-        <v>-46.3686644586537</v>
+        <v>-44.15410676717676</v>
       </c>
       <c r="F101">
-        <v>0.5680726800399204</v>
+        <v>-0.4664819962556045</v>
       </c>
       <c r="G101">
-        <v>-2.398348226106477</v>
+        <v>-2.204409064155627</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>2.108245600239804</v>
       </c>
       <c r="E102">
-        <v>-47.41344318461908</v>
+        <v>-46.12313075834116</v>
       </c>
       <c r="F102">
-        <v>0.7390336297318908</v>
+        <v>-0.573319853664268</v>
       </c>
       <c r="G102">
-        <v>-2.486259828723035</v>
+        <v>-1.911504406989445</v>
       </c>
     </row>
   </sheetData>
